--- a/data/trans_orig/P5B_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5B_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>688</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5680</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99529</t>
+          <t>99603</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104524</t>
+          <t>104521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>111777</t>
+          <t>112176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>214365</t>
+          <t>214385</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>221499</t>
+          <t>221503</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18742</t>
+          <t>19091</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>114371</t>
+          <t>114879</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121927</t>
+          <t>122282</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>129629</t>
+          <t>128898</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>137600</t>
+          <t>137466</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>246965</t>
+          <t>246616</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>258401</t>
+          <t>257938</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4351</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1434</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102348</t>
+          <t>102383</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107249</t>
+          <t>107240</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108222</t>
+          <t>107729</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212905</t>
+          <t>213717</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>218986</t>
+          <t>219291</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15176</t>
+          <t>15904</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>9534</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21860</t>
+          <t>21428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150160</t>
+          <t>149432</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160444</t>
+          <t>160468</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146760</t>
+          <t>147412</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154413</t>
+          <t>154427</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300422</t>
+          <t>300854</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>313008</t>
+          <t>313020</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12821</t>
+          <t>13613</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26356</t>
+          <t>28203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>10573</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22704</t>
+          <t>23863</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27284</t>
+          <t>26612</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>44725</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>477003</t>
+          <t>475156</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>490538</t>
+          <t>489746</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>505845</t>
+          <t>504686</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>518437</t>
+          <t>517976</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>985522</t>
+          <t>987183</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1004624</t>
+          <t>1005296</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>9633</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15413</t>
+          <t>15438</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>120283</t>
+          <t>119701</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>127090</t>
+          <t>127057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>145328</t>
+          <t>144923</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>152557</t>
+          <t>152382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>267624</t>
+          <t>267599</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>278097</t>
+          <t>278054</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101346</t>
+          <t>101815</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111983</t>
+          <t>111523</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>215434</t>
+          <t>215388</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>221127</t>
+          <t>221025</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>11603</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136088</t>
+          <t>136050</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143718</t>
+          <t>143667</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>148099</t>
+          <t>148211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>152836</t>
+          <t>152829</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>286576</t>
+          <t>287137</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>295614</t>
+          <t>295845</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15093</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26127</t>
+          <t>26919</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>460636</t>
+          <t>459603</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>470370</t>
+          <t>470548</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>522941</t>
+          <t>523240</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>532817</t>
+          <t>532717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>986914</t>
+          <t>986122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1001509</t>
+          <t>1001007</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>584</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84997</t>
+          <t>85136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>99767</t>
+          <t>99781</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>188028</t>
+          <t>188788</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>193495</t>
+          <t>193497</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>146759</t>
+          <t>147377</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>169435</t>
+          <t>169323</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>318861</t>
+          <t>319814</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>325542</t>
+          <t>325547</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107463</t>
+          <t>107739</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>113628</t>
+          <t>113672</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126929</t>
+          <t>126764</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>237617</t>
+          <t>237958</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>245804</t>
+          <t>245577</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>789</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159234</t>
+          <t>159213</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165284</t>
+          <t>165312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152470</t>
+          <t>152768</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157602</t>
+          <t>157597</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314883</t>
+          <t>314840</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>322278</t>
+          <t>322185</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15446</t>
+          <t>15144</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22690</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>507503</t>
+          <t>507805</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>517360</t>
+          <t>517515</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>558749</t>
+          <t>558539</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>567061</t>
+          <t>567203</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1070614</t>
+          <t>1071278</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1083167</t>
+          <t>1083334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137628</t>
+          <t>137681</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>254485</t>
+          <t>255091</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>249053</t>
+          <t>248561</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>440045</t>
+          <t>439309</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>97720</t>
+          <t>99992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>879</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120449</t>
+          <t>129080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92681</t>
+          <t>90409</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>189448</t>
+          <t>189482</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>255238</t>
+          <t>246607</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>374844</t>
+          <t>374808</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13768</t>
+          <t>14704</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17940</t>
+          <t>17902</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>160942</t>
+          <t>160674</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>166081</t>
+          <t>166088</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>166527</t>
+          <t>165591</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175841</t>
+          <t>176110</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>329560</t>
+          <t>329598</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>340692</t>
+          <t>340828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110326</t>
+          <t>121356</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134992</t>
+          <t>155409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>555073</t>
+          <t>544043</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>662056</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>743268</t>
+          <t>744313</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>755109</t>
+          <t>754731</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1290737</t>
+          <t>1270320</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1413035</t>
+          <t>1413051</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/P5B_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5B_R-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2499</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6237</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2106</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5606</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6343</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2499</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6113</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>115790</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>112052</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>117682</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,89%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>103103</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>99603</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>104521</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>98866</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>104522</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,67%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,97%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>99,35%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>115790</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>112176</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>117623</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,89%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,83%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>317</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>214385</t>
+          <t>214298</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>221503</t>
+          <t>221453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6490</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3294</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11615</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5805</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2683</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10086</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2665</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10494</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6490</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3276</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11844</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19091</t>
+          <t>18155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>134252</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>129127</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>137448</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,39%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>119160</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>114879</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>122282</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>114471</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>122300</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>134252</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>128898</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>137466</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,39%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>246616</t>
+          <t>247552</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>257938</t>
+          <t>258076</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4330</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2208</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>608</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5465</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5489</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,05%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1207</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4844</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>111366</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>108243</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>105640</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>102383</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>102359</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>107240</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,95%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,93%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>94,91%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,44%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>111366</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>107729</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,7%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>344</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213717</t>
+          <t>213329</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>219291</t>
+          <t>219247</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5723</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2514</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10125</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9157</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4868</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15904</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,54%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5723</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2519</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9534</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>9215</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21428</t>
+          <t>22279</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>151223</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>146821</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>154432</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>156179</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>149432</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>160468</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>149034</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>160019</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,46%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>151223</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>147412</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>154427</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,35%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300854</t>
+          <t>300003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>313020</t>
+          <t>313067</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15919</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9852</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23333</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>19275</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13613</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>28203</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>13041</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>27491</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>15919</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>10573</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>23863</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26612</t>
+          <t>26158</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44725</t>
+          <t>44427</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>512630</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>505216</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>518697</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,59%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,14%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>718</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>484084</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>475156</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>489746</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>475868</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>490318</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,17%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>94,4%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>512630</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>504686</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>517976</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>987183</t>
+          <t>987481</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1005296</t>
+          <t>1005750</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2783,47 +2783,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>97129</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4867</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10047</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4094</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1424</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8780</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8340</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,19%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,83%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4867</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2174</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9633</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>15138</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>149689</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>144509</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>152545</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>124387</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>119701</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>127057</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>120141</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>127076</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,81%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>149689</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>144923</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>152382</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,85%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>267599</t>
+          <t>267899</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>278054</t>
+          <t>278176</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>128481</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>128481</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>128481</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3361,67 +3361,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4976</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>997</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3486</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,95%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1494</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5261</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>879</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>6445</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>115290</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>111808</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,74%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>103854</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>101815</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>101365</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,05%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,67%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>115290</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>111523</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,5%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>338</t>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>215388</t>
+          <t>215189</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>221025</t>
+          <t>220755</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5954</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4545</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1601</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9218</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1537</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9189</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,13%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5261</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>12199</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>151484</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>147518</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>152826</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,12%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>140723</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>136050</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>143667</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>136079</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>143731</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,87%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,9%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>151484</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>148211</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>152829</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,7%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>287137</t>
+          <t>286541</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>295845</t>
+          <t>295771</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>153472</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>153472</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>153472</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>145268</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>145268</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>145268</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>153472</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>153472</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>153472</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8349</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4738</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>14816</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>9636</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5181</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>16126</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5602</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>15733</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,03%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>8349</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4595</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>14072</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>12306</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26919</t>
+          <t>25324</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>755</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>528963</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>522496</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>532574</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,12%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>671</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>466093</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>459603</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>470548</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>459996</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>470127</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,97%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>755</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>528963</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>523240</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>532717</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>986122</t>
+          <t>987717</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1001007</t>
+          <t>1000735</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>537312</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>537312</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>537312</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>685</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>475729</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>475729</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>475729</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>537312</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>537312</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>537312</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3124</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1276</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4949</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4041</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4215</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>103232</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>100872</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>103996</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>88809</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>85136</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>86044</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,58%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,51%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>103232</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>99781</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>103996</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,95%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>261</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>188788</t>
+          <t>188047</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>193497</t>
+          <t>193493</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>103996</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>103996</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>103996</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>103996</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>103996</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>103996</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5523</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1145</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4014</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3493</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5980</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -5073,74 +5073,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>173263</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>169780</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>174725</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,85%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>150246</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>147377</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>147898</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>151391</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,24%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,69%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>173263</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>169323</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>174725</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>501</t>
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>319814</t>
+          <t>318817</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>325547</t>
+          <t>325457</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>151391</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>151391</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>151391</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1475</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5759</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4021</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7633</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7549</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,49%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1475</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6083</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>131372</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>127088</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>111351</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>107739</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>113672</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>107823</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>113693</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,51%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,38%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>131372</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>126764</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>237958</t>
+          <t>237677</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>245577</t>
+          <t>245352</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>115372</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>115372</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>115372</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5859</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2914</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>789</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6888</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7263</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,75%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5440</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>156189</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>152349</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>157599</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,3%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>163187</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>159213</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>165312</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>158838</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>165277</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,25%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>156189</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>152768</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>157597</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314840</t>
+          <t>314314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>322185</t>
+          <t>322259</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166101</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166101</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166101</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3160</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12253</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>9356</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5434</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15144</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5349</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>14758</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6299</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3152</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11816</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>9986</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>22931</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>564056</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>558102</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>567195</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,9%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>771</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>513593</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>507805</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>517515</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>508191</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>517600</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,21%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>564056</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>558539</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>567203</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,9%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1071278</t>
+          <t>1070373</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1083334</t>
+          <t>1083318</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>570355</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>570355</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>570355</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>786</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>522949</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>522949</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>522949</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>824</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>570355</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>570355</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>570355</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,107 +6564,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2731</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2729</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2602</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>125422</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>123395</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>98,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>121071</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>139926</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>137681</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>140412</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>98,06%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>366</t>
@@ -6752,27 +6752,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>257207</t>
+          <t>246493</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>255091</t>
+          <t>244248</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,107 +6907,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5208</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5776</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4881</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5540</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -7020,74 +7020,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>235693</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>231430</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>236638</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,8%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>184413</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>253398</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>248561</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>254337</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>621</t>
@@ -7095,27 +7095,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>443910</t>
+          <t>420105</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>439309</t>
+          <t>416169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>444849</t>
+          <t>421050</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>236638</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>236638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>236638</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>254337</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>254337</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>254337</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>444849</t>
+          <t>421050</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>444849</t>
+          <t>421050</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>444849</t>
+          <t>421050</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>28229</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>919</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>99992</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,83%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>52,52%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16914</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>28229</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>863</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129080</t>
+          <t>16505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>162172</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>90409</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>189482</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>85,17%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>47,48%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>152920</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>140136</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>156337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>347458</t>
+          <t>321261</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>246607</t>
+          <t>308886</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>374808</t>
+          <t>324528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7833</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4423</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13426</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3053</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1118</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6532</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8317</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14704</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,17 +7668,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>10947</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17902</t>
+          <t>17613</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>160586</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>154993</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>163996</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>164153</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>160674</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>166088</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,17%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>171978</t>
+          <t>163211</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>165591</t>
+          <t>159713</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176110</t>
+          <t>165229</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,17 +7781,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>336130</t>
+          <t>323798</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>329598</t>
+          <t>317132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>340828</t>
+          <t>328066</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167206</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167206</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167206</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>166325</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>166325</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>166325</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>347500</t>
+          <t>334745</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>347500</t>
+          <t>334745</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>347500</t>
+          <t>334745</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9262</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4997</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15865</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>31282</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>121356</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18,24%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41023</t>
+          <t>16506</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12678</t>
+          <t>9948</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155409</t>
+          <t>27531</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>690042</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>683439</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>694307</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>934</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>634117</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>544043</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>662139</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>81,76%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>962</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>750589</t>
+          <t>621615</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>744313</t>
+          <t>610960</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754731</t>
+          <t>625718</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1384706</t>
+          <t>1311657</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1270320</t>
+          <t>1300632</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1413051</t>
+          <t>1318215</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699304</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699304</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699304</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665399</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665399</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665399</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760330</t>
+          <t>628859</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760330</t>
+          <t>628859</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760330</t>
+          <t>628859</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425729</t>
+          <t>1328163</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425729</t>
+          <t>1328163</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425729</t>
+          <t>1328163</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
